--- a/results/part4_pricing/pricing_results.xlsx
+++ b/results/part4_pricing/pricing_results.xlsx
@@ -8,13 +8,10 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Rulebook" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price_Plan" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_By_Product" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROI_Impact" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sensitivity" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_And_Credit_Actions" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Safety_Checks" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Price_Plan" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Plan_By_Product" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ROI_And_Sensitivity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Stock_And_Credit_Actions" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -67,7 +64,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -76,12 +73,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -704,959 +695,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E42"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
-    <col width="90" customWidth="1" min="3" max="3"/>
-    <col width="100" customWidth="1" min="4" max="4"/>
-    <col width="45" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Rules</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="4" t="inlineStr">
-        <is>
-          <t>rule</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="C2" s="4" t="inlineStr">
-        <is>
-          <t>in plain words</t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="inlineStr">
-        <is>
-          <t>math</t>
-        </is>
-      </c>
-      <c r="E2" s="4" t="inlineStr">
-        <is>
-          <t>parameters</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Scarcity premium</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>The more of the expected demand we cannot serve, the more we charge; peak season uses the full premium, quiet seasons less.</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>w = min(1, g/0.30) if g &gt; 5% else 0;  u = 8% x w x m(season);  m = 1.00 / 0.75 / 0.50 (peak / normal / off-peak)</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>U_MAX, GAP_MIN, G_FULL, SEASON_MULT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>Rule 2</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Sell-out protection</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Raise the price only as far as we would still sell (almost) the same units even if customers were twice as price-sensitive as assumed.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>largest M &lt;= 1+u with E[min(D*M^-2, S)] &gt;= 99% of E[min(D, S)]  (1,000 simulated demand/stock pairs)</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>EPS_STRESS, VOL_TOL, SIM_N</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>Rule 3</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Surplus &amp; clearance</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Markdown only for products with more than 26 weeks of stock and no scarcity; deeper with more excess, only in quiet weeks, and only if it pays for itself.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>cover = S/D;  d = 10% x min(1, ln(cover/26)/ln(4)) x lull(season);  apply if Profit(P0(1-d); eps=-1) &gt; Profit(P0; eps=-1)</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D_MAX, COVER_MAX, COVER_FULL, LULL, EPS_PLAN, CARRY_ANNUAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>Rule 4</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Credit-risk rule</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>A/B unchanged; C markdown at most 5%; D/E no markdowns, a risk premium and shorter payment terms.</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>premium = share_on_credit x default_rate + DSO/365 x 8%;  target x (1 + premium)</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>MD_CAP_C, FUND_RATE, TERMS_CUT_DAYS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>Rule 5</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Guardrails</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Price never below cost + minimum markup + carrying cost + expected credit loss; inside the competitive band; moves at most 3% per week.</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>floor = COGS(1+5%+12%*4/52)/(1-ecl);  0.92 P0 &lt;= price &lt;= 1.10 P0;  |price_t / price_(t-1) - 1| &lt;= 3%</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>MIN_MARKUP, CARRY_ANNUAL, BAND_UP, BAND_DOWN, STEP_MAX</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>Rule 6</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Final price</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>Combine the rules, then apply the guardrails in order.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>target = P0 (1+u_protected)(1+premium)(1-d) -&gt; floor -&gt; band -&gt; weekly step</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n"/>
-      <c r="B9" s="2" t="n"/>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="5" t="inlineStr">
-        <is>
-          <t>Parameters (defaults)</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="n"/>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n"/>
-      <c r="E10" s="2" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="4" t="inlineStr">
-        <is>
-          <t>parameter</t>
-        </is>
-      </c>
-      <c r="B11" s="4" t="inlineStr">
-        <is>
-          <t>default</t>
-        </is>
-      </c>
-      <c r="C11" s="4" t="inlineStr">
-        <is>
-          <t>meaning (plain words)</t>
-        </is>
-      </c>
-      <c r="D11" s="4" t="inlineStr">
-        <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="inlineStr">
-        <is>
-          <t>used in</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>U_MAX</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>Largest scarcity premium</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>GAP_MIN</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>Unserved-demand share below which stock is not a constraint</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>G_FULL</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Unserved-demand share at which the premium is maximal</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>SEASON_MULT</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>peak 1.00 / normal 0.75 / off-peak 0.50</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>Share of the premium used in peak / normal / off-peak weeks</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>PEAK_IDX / OFFPEAK_IDX</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>1.1 / 0.9</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Seasonal-curve levels that define peak and off-peak weeks</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>data-derived</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1/3</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>EPS_PLAN</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>Planning price sensitivity (-1 = demand falls 1% when price rises 1%)</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Rule 3, ROI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>EPS_STRESS</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>Stress price sensitivity used by the sell-out protection</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Rule 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>VOL_TOL</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Units we accept to lose because of a scarcity premium</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Rule 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>D_MAX / COVER_MAX / COVER_FULL</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>0.1 / 26 / 104</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>Largest markdown; weeks of cover where markdowns start / are deepest</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Rule 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>LULL</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>off-peak 1.0 / normal 0.5 / peak 0</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Share of the markdown used in off-peak / normal / peak weeks</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Rule 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>MD_CAP_C</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Markdown cap for rating C</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Rule 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>TERMS_CUT_DAYS</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="n">
-        <v>15</v>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>Recommended payment-terms cut for rating D/E</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Rule 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>FUND_RATE</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>Annual cost of money tied up in unpaid invoices</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>Rule 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>MIN_MARKUP</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>Minimum markup on cost in the price floor</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Rule 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CARRY_ANNUAL</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>Annual cost of holding stock, as share of cost</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>Rule 3/5</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CARRY_FLOOR_WEEKS</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>Weeks of carrying cost included in the floor</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Rule 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>BAND_UP / BAND_DOWN</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>+0.1 / -0.08</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>Competitive band around the reference price (no competitor data: proxy)</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Rule 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>STEP_MAX</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Largest price change from one week to the next</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>policy</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>Rule 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>SIM_N / SEED</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>1000 / 42</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>Simulation draws per product-week; random seed</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>technical</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>Rule 1-3</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="n"/>
-      <c r="B31" s="2" t="n"/>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n"/>
-      <c r="E31" s="2" t="n"/>
-    </row>
-    <row r="32">
-      <c r="A32" s="5" t="inlineStr">
-        <is>
-          <t>Assumptions</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="n"/>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n"/>
-      <c r="E32" s="2" t="n"/>
-    </row>
-    <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>#</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>topic</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>assumption</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n"/>
-      <c r="E33" s="2" t="n"/>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>A1</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>Price sensitivity</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>Unknown. Planning case -1, stress case -2, results shown for 0 ... -3. A pilot should replace this.</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="n"/>
-      <c r="E34" s="2" t="n"/>
-    </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>Competitor prices</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>Not in the data. The 13-week average price +/- the band is the proxy for the market.</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="n"/>
-      <c r="E35" s="2" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>Credit layer</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>Ratings, DSO and default rates come from the Part 3 assumptions (not customer data).</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="n"/>
-      <c r="E36" s="2" t="n"/>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>A4</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Future stock</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>Unknown. Simulated from each product's own last 104 weeks of stock (the same approach as Part 2).</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="n"/>
-      <c r="E37" s="2" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>A5</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>Demand</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>Part 2 forecast with a lognormal spread read from its P10-P90 band; replay uses reconstructed demand, which is an estimate in stock-limited weeks.</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="n"/>
-      <c r="E38" s="2" t="n"/>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>Cost</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>Unit cost held at its last-13-week average; no cost changes assumed.</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="n"/>
-      <c r="E39" s="2" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>A7</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>Carrying cost and funding</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>12% of cost per year for holding stock; 8% per year for money tied up in receivables (assumptions).</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="n"/>
-      <c r="E40" s="2" t="n"/>
-    </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>A8</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>Holding today's reference price; demand at that price equals the forecast.</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="n"/>
-      <c r="E41" s="2" t="n"/>
-    </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>A9</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>Scope</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>Prices are recommendations per product-week; customer-specific or channel-specific pricing is out of scope (no customer data).</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="n"/>
-      <c r="E42" s="2" t="n"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:X781"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -70093,7 +69131,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -71851,417 +70889,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I15"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="29" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="11" customWidth="1" min="3" max="3"/>
-    <col width="12" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="28" customWidth="1" min="8" max="8"/>
-    <col width="26" customWidth="1" min="9" max="9"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="3" t="inlineStr">
-        <is>
-          <t>Next 26 weeks (forecast): engine vs holding today's price, by customer reaction</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t>eps</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t>d_units_%</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t>d_revenue</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t>d_gross_profit</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit_%</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit_scarcity_only</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit_credit_rule</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>very high sensitivity</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C3" t="n">
-        <v>-1.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>676012.78</v>
-      </c>
-      <c r="E3" t="n">
-        <v>1159591.24</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1154884.9</v>
-      </c>
-      <c r="G3" t="n">
-        <v>15.5</v>
-      </c>
-      <c r="H3" t="n">
-        <v>1063621.22</v>
-      </c>
-      <c r="I3" t="n">
-        <v>91263.67999999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>high sensitivity</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C4" t="n">
-        <v>-0.95</v>
-      </c>
-      <c r="D4" t="n">
-        <v>935995.77</v>
-      </c>
-      <c r="E4" t="n">
-        <v>1223981.43</v>
-      </c>
-      <c r="F4" t="n">
-        <v>1216613.87</v>
-      </c>
-      <c r="G4" t="n">
-        <v>16.33</v>
-      </c>
-      <c r="H4" t="n">
-        <v>1100720.38</v>
-      </c>
-      <c r="I4" t="n">
-        <v>115893.49</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>planning case</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C5" t="n">
-        <v>-0.44</v>
-      </c>
-      <c r="D5" t="n">
-        <v>1138413.09</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1273117.85</v>
-      </c>
-      <c r="F5" t="n">
-        <v>1263583.5</v>
-      </c>
-      <c r="G5" t="n">
-        <v>16.96</v>
-      </c>
-      <c r="H5" t="n">
-        <v>1125373.09</v>
-      </c>
-      <c r="I5" t="n">
-        <v>138210.4</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>low sensitivity</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C6" t="n">
-        <v>-0.21</v>
-      </c>
-      <c r="D6" t="n">
-        <v>1229274.3</v>
-      </c>
-      <c r="E6" t="n">
-        <v>1294995.78</v>
-      </c>
-      <c r="F6" t="n">
-        <v>1284473.94</v>
-      </c>
-      <c r="G6" t="n">
-        <v>17.24</v>
-      </c>
-      <c r="H6" t="n">
-        <v>1135713.35</v>
-      </c>
-      <c r="I6" t="n">
-        <v>148760.59</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>customers ignore price</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>0</v>
-      </c>
-      <c r="C7" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" t="n">
-        <v>1315745.93</v>
-      </c>
-      <c r="E7" t="n">
-        <v>1315745.93</v>
-      </c>
-      <c r="F7" t="n">
-        <v>1304279.56</v>
-      </c>
-      <c r="G7" t="n">
-        <v>17.51</v>
-      </c>
-      <c r="H7" t="n">
-        <v>1145272.08</v>
-      </c>
-      <c r="I7" t="n">
-        <v>159007.48</v>
-      </c>
-    </row>
-    <row r="8"/>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>Replay of the last 52 weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>scenario</t>
-        </is>
-      </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>eps</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>d_units_%</t>
-        </is>
-      </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>d_revenue</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>d_gross_profit</t>
-        </is>
-      </c>
-      <c r="F10" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit</t>
-        </is>
-      </c>
-      <c r="G10" s="1" t="inlineStr">
-        <is>
-          <t>d_net_profit_%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>very high sensitivity</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C11" t="n">
-        <v>-1.58</v>
-      </c>
-      <c r="D11" t="n">
-        <v>428942.52</v>
-      </c>
-      <c r="E11" t="n">
-        <v>1268378.55</v>
-      </c>
-      <c r="F11" t="n">
-        <v>1266606.2</v>
-      </c>
-      <c r="G11" t="n">
-        <v>9.41</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>high sensitivity</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C12" t="n">
-        <v>-1.03</v>
-      </c>
-      <c r="D12" t="n">
-        <v>808742.36</v>
-      </c>
-      <c r="E12" t="n">
-        <v>1357428.87</v>
-      </c>
-      <c r="F12" t="n">
-        <v>1351500.01</v>
-      </c>
-      <c r="G12" t="n">
-        <v>10.04</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>planning case</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C13" t="n">
-        <v>-0.51</v>
-      </c>
-      <c r="D13" t="n">
-        <v>1168598.25</v>
-      </c>
-      <c r="E13" t="n">
-        <v>1441315.01</v>
-      </c>
-      <c r="F13" t="n">
-        <v>1431372.38</v>
-      </c>
-      <c r="G13" t="n">
-        <v>10.64</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>low sensitivity</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>-0.5</v>
-      </c>
-      <c r="C14" t="n">
-        <v>-0.26</v>
-      </c>
-      <c r="D14" t="n">
-        <v>1346080.27</v>
-      </c>
-      <c r="E14" t="n">
-        <v>1482629.65</v>
-      </c>
-      <c r="F14" t="n">
-        <v>1470710.41</v>
-      </c>
-      <c r="G14" t="n">
-        <v>10.93</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>customers ignore price</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>0</v>
-      </c>
-      <c r="C15" t="n">
-        <v>0</v>
-      </c>
-      <c r="D15" t="n">
-        <v>1524041.73</v>
-      </c>
-      <c r="E15" t="n">
-        <v>1524041.73</v>
-      </c>
-      <c r="F15" t="n">
-        <v>1510140.47</v>
-      </c>
-      <c r="G15" t="n">
-        <v>11.22</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:H26"/>
+  <dimension ref="A1:I42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="60" customWidth="1" min="1" max="1"/>
@@ -72271,693 +70905,1074 @@
     <col width="20" customWidth="1" min="5" max="5"/>
     <col width="20" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
-    <col width="25" customWidth="1" min="8" max="8"/>
+    <col width="28" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
-          <t>One setting at a time: 26-week profit gain by customer reaction</t>
+          <t>Next 26 weeks (forecast): engine vs holding today's price, by customer reaction</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>setting</t>
+          <t>scenario</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>value</t>
+          <t>eps</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>is_default</t>
+          <t>d_units_%</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
         <is>
-          <t>eps=0</t>
+          <t>d_revenue</t>
         </is>
       </c>
       <c r="E2" s="1" t="inlineStr">
         <is>
-          <t>eps=-0.5</t>
+          <t>d_gross_profit</t>
         </is>
       </c>
       <c r="F2" s="1" t="inlineStr">
         <is>
-          <t>eps=-1</t>
+          <t>d_net_profit</t>
         </is>
       </c>
       <c r="G2" s="1" t="inlineStr">
         <is>
-          <t>eps=-2</t>
+          <t>d_net_profit_%</t>
         </is>
       </c>
       <c r="H2" s="1" t="inlineStr">
         <is>
-          <t>eps=-3</t>
+          <t>d_net_profit_scarcity_only</t>
+        </is>
+      </c>
+      <c r="I2" s="1" t="inlineStr">
+        <is>
+          <t>d_net_profit_credit_rule</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>U_MAX (largest premium)</t>
+          <t>very high sensitivity</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="C3" t="b">
-        <v>0</v>
+        <v>-3</v>
+      </c>
+      <c r="C3" t="n">
+        <v>-1.6</v>
       </c>
       <c r="D3" t="n">
-        <v>873686</v>
+        <v>676012.78</v>
       </c>
       <c r="E3" t="n">
-        <v>854448</v>
+        <v>1159591.24</v>
       </c>
       <c r="F3" t="n">
-        <v>834547</v>
+        <v>1154884.9</v>
       </c>
       <c r="G3" t="n">
-        <v>792267</v>
+        <v>15.5</v>
       </c>
       <c r="H3" t="n">
-        <v>745643</v>
+        <v>1063621.22</v>
+      </c>
+      <c r="I3" t="n">
+        <v>91263.67999999999</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U_MAX (largest premium)</t>
+          <t>high sensitivity</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="C4" t="b">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="C4" t="n">
+        <v>-0.95</v>
       </c>
       <c r="D4" t="n">
-        <v>1107791</v>
+        <v>935995.77</v>
       </c>
       <c r="E4" t="n">
-        <v>1088128</v>
+        <v>1223981.43</v>
       </c>
       <c r="F4" t="n">
-        <v>1067542</v>
+        <v>1216613.87</v>
       </c>
       <c r="G4" t="n">
-        <v>1022496</v>
+        <v>16.33</v>
       </c>
       <c r="H4" t="n">
-        <v>968706</v>
+        <v>1100720.38</v>
+      </c>
+      <c r="I4" t="n">
+        <v>115893.49</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>U_MAX (largest premium)</t>
+          <t>planning case</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="C5" t="b">
-        <v>1</v>
+        <v>-1</v>
+      </c>
+      <c r="C5" t="n">
+        <v>-0.44</v>
       </c>
       <c r="D5" t="n">
-        <v>1304280</v>
+        <v>1138413.09</v>
       </c>
       <c r="E5" t="n">
-        <v>1284474</v>
+        <v>1273117.85</v>
       </c>
       <c r="F5" t="n">
-        <v>1263583</v>
+        <v>1263583.5</v>
       </c>
       <c r="G5" t="n">
-        <v>1216614</v>
+        <v>16.96</v>
       </c>
       <c r="H5" t="n">
-        <v>1154885</v>
+        <v>1125373.09</v>
+      </c>
+      <c r="I5" t="n">
+        <v>138210.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>U_MAX (largest premium)</t>
+          <t>low sensitivity</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.1</v>
-      </c>
-      <c r="C6" t="b">
-        <v>0</v>
+        <v>-0.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>-0.21</v>
       </c>
       <c r="D6" t="n">
-        <v>1468652</v>
+        <v>1229274.3</v>
       </c>
       <c r="E6" t="n">
-        <v>1448803</v>
+        <v>1294995.78</v>
       </c>
       <c r="F6" t="n">
-        <v>1427764</v>
+        <v>1284473.94</v>
       </c>
       <c r="G6" t="n">
-        <v>1378931</v>
+        <v>17.24</v>
       </c>
       <c r="H6" t="n">
-        <v>1305425</v>
+        <v>1135713.35</v>
+      </c>
+      <c r="I6" t="n">
+        <v>148760.59</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G_FULL (scarcity at full premium)</t>
+          <t>customers ignore price</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.2</v>
-      </c>
-      <c r="C7" t="b">
+        <v>0</v>
+      </c>
+      <c r="C7" t="n">
         <v>0</v>
       </c>
       <c r="D7" t="n">
-        <v>1304280</v>
+        <v>1315745.93</v>
       </c>
       <c r="E7" t="n">
-        <v>1284474</v>
+        <v>1315745.93</v>
       </c>
       <c r="F7" t="n">
-        <v>1263583</v>
+        <v>1304279.56</v>
       </c>
       <c r="G7" t="n">
-        <v>1216614</v>
+        <v>17.51</v>
       </c>
       <c r="H7" t="n">
-        <v>1154885</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>G_FULL (scarcity at full premium)</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="C8" t="b">
-        <v>1</v>
-      </c>
-      <c r="D8" t="n">
-        <v>1304280</v>
-      </c>
-      <c r="E8" t="n">
-        <v>1284474</v>
-      </c>
-      <c r="F8" t="n">
-        <v>1263583</v>
-      </c>
-      <c r="G8" t="n">
-        <v>1216614</v>
-      </c>
-      <c r="H8" t="n">
-        <v>1154885</v>
-      </c>
-    </row>
+        <v>1145272.08</v>
+      </c>
+      <c r="I7" t="n">
+        <v>159007.48</v>
+      </c>
+    </row>
+    <row r="8"/>
     <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>G_FULL (scarcity at full premium)</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="C9" t="b">
-        <v>0</v>
-      </c>
-      <c r="D9" t="n">
-        <v>1301990</v>
-      </c>
-      <c r="E9" t="n">
-        <v>1282194</v>
-      </c>
-      <c r="F9" t="n">
-        <v>1261324</v>
-      </c>
-      <c r="G9" t="n">
-        <v>1214505</v>
-      </c>
-      <c r="H9" t="n">
-        <v>1153246</v>
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Replay of the last 52 weeks</t>
+        </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>STEP_MAX (weekly step)</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="C10" t="b">
-        <v>0</v>
-      </c>
-      <c r="D10" t="n">
-        <v>1288694</v>
-      </c>
-      <c r="E10" t="n">
-        <v>1269075</v>
-      </c>
-      <c r="F10" t="n">
-        <v>1248387</v>
-      </c>
-      <c r="G10" t="n">
-        <v>1201977</v>
-      </c>
-      <c r="H10" t="n">
-        <v>1141184</v>
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>scenario</t>
+        </is>
+      </c>
+      <c r="B10" s="1" t="inlineStr">
+        <is>
+          <t>eps</t>
+        </is>
+      </c>
+      <c r="C10" s="1" t="inlineStr">
+        <is>
+          <t>d_units_%</t>
+        </is>
+      </c>
+      <c r="D10" s="1" t="inlineStr">
+        <is>
+          <t>d_revenue</t>
+        </is>
+      </c>
+      <c r="E10" s="1" t="inlineStr">
+        <is>
+          <t>d_gross_profit</t>
+        </is>
+      </c>
+      <c r="F10" s="1" t="inlineStr">
+        <is>
+          <t>d_net_profit</t>
+        </is>
+      </c>
+      <c r="G10" s="1" t="inlineStr">
+        <is>
+          <t>d_net_profit_%</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STEP_MAX (weekly step)</t>
+          <t>very high sensitivity</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C11" t="b">
-        <v>1</v>
+        <v>-3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-1.58</v>
       </c>
       <c r="D11" t="n">
-        <v>1304280</v>
+        <v>428942.52</v>
       </c>
       <c r="E11" t="n">
-        <v>1284474</v>
+        <v>1268378.55</v>
       </c>
       <c r="F11" t="n">
-        <v>1263583</v>
+        <v>1266606.2</v>
       </c>
       <c r="G11" t="n">
-        <v>1216614</v>
-      </c>
-      <c r="H11" t="n">
-        <v>1154885</v>
+        <v>9.41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STEP_MAX (weekly step)</t>
+          <t>high sensitivity</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.05</v>
-      </c>
-      <c r="C12" t="b">
-        <v>0</v>
+        <v>-2</v>
+      </c>
+      <c r="C12" t="n">
+        <v>-1.03</v>
       </c>
       <c r="D12" t="n">
-        <v>1313407</v>
+        <v>808742.36</v>
       </c>
       <c r="E12" t="n">
-        <v>1293565</v>
+        <v>1357428.87</v>
       </c>
       <c r="F12" t="n">
-        <v>1272621</v>
+        <v>1351500.01</v>
       </c>
       <c r="G12" t="n">
-        <v>1225435</v>
-      </c>
-      <c r="H12" t="n">
-        <v>1163249</v>
+        <v>10.04</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>VOL_TOL (units we accept to lose)</t>
+          <t>planning case</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0</v>
-      </c>
-      <c r="C13" t="b">
-        <v>0</v>
+        <v>-1</v>
+      </c>
+      <c r="C13" t="n">
+        <v>-0.51</v>
       </c>
       <c r="D13" t="n">
-        <v>654143</v>
+        <v>1168598.25</v>
       </c>
       <c r="E13" t="n">
-        <v>644526</v>
+        <v>1441315.01</v>
       </c>
       <c r="F13" t="n">
-        <v>634836</v>
+        <v>1431372.38</v>
       </c>
       <c r="G13" t="n">
-        <v>615255</v>
-      </c>
-      <c r="H13" t="n">
-        <v>595100</v>
+        <v>10.64</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>VOL_TOL (units we accept to lose)</t>
+          <t>low sensitivity</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="C14" t="b">
-        <v>1</v>
+        <v>-0.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>-0.26</v>
       </c>
       <c r="D14" t="n">
-        <v>1304280</v>
+        <v>1346080.27</v>
       </c>
       <c r="E14" t="n">
-        <v>1284474</v>
+        <v>1482629.65</v>
       </c>
       <c r="F14" t="n">
-        <v>1263583</v>
+        <v>1470710.41</v>
       </c>
       <c r="G14" t="n">
-        <v>1216614</v>
-      </c>
-      <c r="H14" t="n">
-        <v>1154885</v>
+        <v>10.93</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>VOL_TOL (units we accept to lose)</t>
+          <t>customers ignore price</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.03</v>
-      </c>
-      <c r="C15" t="b">
+        <v>0</v>
+      </c>
+      <c r="C15" t="n">
         <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>1723221</v>
+        <v>1524041.73</v>
       </c>
       <c r="E15" t="n">
-        <v>1682061</v>
+        <v>1524041.73</v>
       </c>
       <c r="F15" t="n">
-        <v>1637722</v>
+        <v>1510140.47</v>
       </c>
       <c r="G15" t="n">
-        <v>1534286</v>
-      </c>
-      <c r="H15" t="n">
-        <v>1401623</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>EPS_STRESS (protection strictness)</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>-1</v>
-      </c>
-      <c r="C16" t="b">
-        <v>0</v>
-      </c>
-      <c r="D16" t="n">
-        <v>1590254</v>
-      </c>
-      <c r="E16" t="n">
-        <v>1558317</v>
-      </c>
-      <c r="F16" t="n">
-        <v>1523664</v>
-      </c>
-      <c r="G16" t="n">
-        <v>1441299</v>
-      </c>
-      <c r="H16" t="n">
-        <v>1332126</v>
-      </c>
-    </row>
+        <v>11.22</v>
+      </c>
+    </row>
+    <row r="16"/>
     <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>EPS_STRESS (protection strictness)</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>-2</v>
-      </c>
-      <c r="C17" t="b">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>One setting at a time: 26-week profit gain by customer reaction</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>setting</t>
+        </is>
+      </c>
+      <c r="B18" s="1" t="inlineStr">
+        <is>
+          <t>value</t>
+        </is>
+      </c>
+      <c r="C18" s="1" t="inlineStr">
+        <is>
+          <t>is_default</t>
+        </is>
+      </c>
+      <c r="D18" s="1" t="inlineStr">
+        <is>
+          <t>eps=0</t>
+        </is>
+      </c>
+      <c r="E18" s="1" t="inlineStr">
+        <is>
+          <t>eps=-0.5</t>
+        </is>
+      </c>
+      <c r="F18" s="1" t="inlineStr">
+        <is>
+          <t>eps=-1</t>
+        </is>
+      </c>
+      <c r="G18" s="1" t="inlineStr">
+        <is>
+          <t>eps=-2</t>
+        </is>
+      </c>
+      <c r="H18" s="1" t="inlineStr">
+        <is>
+          <t>eps=-3</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>U_MAX (largest premium)</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="C19" t="b">
+        <v>0</v>
+      </c>
+      <c r="D19" t="n">
+        <v>873686</v>
+      </c>
+      <c r="E19" t="n">
+        <v>854448</v>
+      </c>
+      <c r="F19" t="n">
+        <v>834547</v>
+      </c>
+      <c r="G19" t="n">
+        <v>792267</v>
+      </c>
+      <c r="H19" t="n">
+        <v>745643</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>U_MAX (largest premium)</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="C20" t="b">
+        <v>0</v>
+      </c>
+      <c r="D20" t="n">
+        <v>1107791</v>
+      </c>
+      <c r="E20" t="n">
+        <v>1088128</v>
+      </c>
+      <c r="F20" t="n">
+        <v>1067542</v>
+      </c>
+      <c r="G20" t="n">
+        <v>1022496</v>
+      </c>
+      <c r="H20" t="n">
+        <v>968706</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>U_MAX (largest premium)</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="C21" t="b">
         <v>1</v>
       </c>
-      <c r="D17" t="n">
+      <c r="D21" t="n">
         <v>1304280</v>
       </c>
-      <c r="E17" t="n">
+      <c r="E21" t="n">
         <v>1284474</v>
       </c>
-      <c r="F17" t="n">
+      <c r="F21" t="n">
         <v>1263583</v>
       </c>
-      <c r="G17" t="n">
+      <c r="G21" t="n">
         <v>1216614</v>
       </c>
-      <c r="H17" t="n">
+      <c r="H21" t="n">
         <v>1154885</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>EPS_STRESS (protection strictness)</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>-3</v>
-      </c>
-      <c r="C18" t="b">
-        <v>0</v>
-      </c>
-      <c r="D18" t="n">
-        <v>1146622</v>
-      </c>
-      <c r="E18" t="n">
-        <v>1131207</v>
-      </c>
-      <c r="F18" t="n">
-        <v>1115256</v>
-      </c>
-      <c r="G18" t="n">
-        <v>1081013</v>
-      </c>
-      <c r="H18" t="n">
-        <v>1040000</v>
-      </c>
-    </row>
-    <row r="19"/>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>If true demand is lower than our estimate</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>true demand vs estimate</t>
-        </is>
-      </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>profit gain eps=0</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>profit gain eps=-0.5</t>
-        </is>
-      </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>profit gain eps=-1</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>profit gain eps=-2</t>
-        </is>
-      </c>
-      <c r="F21" s="1" t="inlineStr">
-        <is>
-          <t>profit gain eps=-3</t>
-        </is>
-      </c>
-      <c r="G21" s="1" t="inlineStr">
-        <is>
-          <t>units change % (eps=-1)</t>
-        </is>
-      </c>
-      <c r="H21" s="1" t="inlineStr">
-        <is>
-          <t>units change % (eps=-2)</t>
-        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>U_MAX (largest premium)</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1304279.56</v>
-      </c>
-      <c r="C22" t="n">
-        <v>1284473.94</v>
+        <v>0.1</v>
+      </c>
+      <c r="C22" t="b">
+        <v>0</v>
       </c>
       <c r="D22" t="n">
-        <v>1263583.5</v>
+        <v>1468652</v>
       </c>
       <c r="E22" t="n">
-        <v>1216613.87</v>
+        <v>1448803</v>
       </c>
       <c r="F22" t="n">
-        <v>1154884.9</v>
+        <v>1427764</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.44</v>
+        <v>1378931</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.95</v>
+        <v>1305425</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>80%</t>
+          <t>G_FULL (scarcity at full premium)</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>1252515.09</v>
-      </c>
-      <c r="C23" t="n">
-        <v>1207385.1</v>
+        <v>0.2</v>
+      </c>
+      <c r="C23" t="b">
+        <v>0</v>
       </c>
       <c r="D23" t="n">
-        <v>1155260.79</v>
+        <v>1304280</v>
       </c>
       <c r="E23" t="n">
-        <v>1028408.74</v>
+        <v>1284474</v>
       </c>
       <c r="F23" t="n">
-        <v>872702.01</v>
+        <v>1263583</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.14</v>
+        <v>1216614</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.66</v>
+        <v>1154885</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>G_FULL (scarcity at full premium)</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1104625.19</v>
-      </c>
-      <c r="C24" t="n">
-        <v>1021392.17</v>
+        <v>0.3</v>
+      </c>
+      <c r="C24" t="b">
+        <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>938688.7</v>
+        <v>1304280</v>
       </c>
       <c r="E24" t="n">
-        <v>775772.13</v>
+        <v>1284474</v>
       </c>
       <c r="F24" t="n">
-        <v>610863.35</v>
+        <v>1263583</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.37</v>
+        <v>1216614</v>
       </c>
       <c r="H24" t="n">
-        <v>-4.7</v>
+        <v>1154885</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>50%</t>
+          <t>G_FULL (scarcity at full premium)</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>989526.74</v>
-      </c>
-      <c r="C25" t="n">
-        <v>904836.48</v>
+        <v>0.5</v>
+      </c>
+      <c r="C25" t="b">
+        <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>817978.41</v>
+        <v>1301990</v>
       </c>
       <c r="E25" t="n">
-        <v>635405.22</v>
+        <v>1282194</v>
       </c>
       <c r="F25" t="n">
-        <v>439124.85</v>
+        <v>1261324</v>
       </c>
       <c r="G25" t="n">
-        <v>-2.78</v>
+        <v>1214505</v>
       </c>
       <c r="H25" t="n">
-        <v>-5.74</v>
+        <v>1153246</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
+          <t>STEP_MAX (weekly step)</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="C26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>1288694</v>
+      </c>
+      <c r="E26" t="n">
+        <v>1269075</v>
+      </c>
+      <c r="F26" t="n">
+        <v>1248387</v>
+      </c>
+      <c r="G26" t="n">
+        <v>1201977</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1141184</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>STEP_MAX (weekly step)</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C27" t="b">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>1304280</v>
+      </c>
+      <c r="E27" t="n">
+        <v>1284474</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1263583</v>
+      </c>
+      <c r="G27" t="n">
+        <v>1216614</v>
+      </c>
+      <c r="H27" t="n">
+        <v>1154885</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>STEP_MAX (weekly step)</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="C28" t="b">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>1313407</v>
+      </c>
+      <c r="E28" t="n">
+        <v>1293565</v>
+      </c>
+      <c r="F28" t="n">
+        <v>1272621</v>
+      </c>
+      <c r="G28" t="n">
+        <v>1225435</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1163249</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>VOL_TOL (units we accept to lose)</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="b">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>654143</v>
+      </c>
+      <c r="E29" t="n">
+        <v>644526</v>
+      </c>
+      <c r="F29" t="n">
+        <v>634836</v>
+      </c>
+      <c r="G29" t="n">
+        <v>615255</v>
+      </c>
+      <c r="H29" t="n">
+        <v>595100</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>VOL_TOL (units we accept to lose)</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="C30" t="b">
+        <v>1</v>
+      </c>
+      <c r="D30" t="n">
+        <v>1304280</v>
+      </c>
+      <c r="E30" t="n">
+        <v>1284474</v>
+      </c>
+      <c r="F30" t="n">
+        <v>1263583</v>
+      </c>
+      <c r="G30" t="n">
+        <v>1216614</v>
+      </c>
+      <c r="H30" t="n">
+        <v>1154885</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>VOL_TOL (units we accept to lose)</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="C31" t="b">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>1723221</v>
+      </c>
+      <c r="E31" t="n">
+        <v>1682061</v>
+      </c>
+      <c r="F31" t="n">
+        <v>1637722</v>
+      </c>
+      <c r="G31" t="n">
+        <v>1534286</v>
+      </c>
+      <c r="H31" t="n">
+        <v>1401623</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EPS_STRESS (protection strictness)</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>-1</v>
+      </c>
+      <c r="C32" t="b">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>1590254</v>
+      </c>
+      <c r="E32" t="n">
+        <v>1558317</v>
+      </c>
+      <c r="F32" t="n">
+        <v>1523664</v>
+      </c>
+      <c r="G32" t="n">
+        <v>1441299</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1332126</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EPS_STRESS (protection strictness)</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C33" t="b">
+        <v>1</v>
+      </c>
+      <c r="D33" t="n">
+        <v>1304280</v>
+      </c>
+      <c r="E33" t="n">
+        <v>1284474</v>
+      </c>
+      <c r="F33" t="n">
+        <v>1263583</v>
+      </c>
+      <c r="G33" t="n">
+        <v>1216614</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1154885</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EPS_STRESS (protection strictness)</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C34" t="b">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>1146622</v>
+      </c>
+      <c r="E34" t="n">
+        <v>1131207</v>
+      </c>
+      <c r="F34" t="n">
+        <v>1115256</v>
+      </c>
+      <c r="G34" t="n">
+        <v>1081013</v>
+      </c>
+      <c r="H34" t="n">
+        <v>1040000</v>
+      </c>
+    </row>
+    <row r="35"/>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>If true demand is lower than our estimate</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>true demand vs estimate</t>
+        </is>
+      </c>
+      <c r="B37" s="1" t="inlineStr">
+        <is>
+          <t>profit gain eps=0</t>
+        </is>
+      </c>
+      <c r="C37" s="1" t="inlineStr">
+        <is>
+          <t>profit gain eps=-0.5</t>
+        </is>
+      </c>
+      <c r="D37" s="1" t="inlineStr">
+        <is>
+          <t>profit gain eps=-1</t>
+        </is>
+      </c>
+      <c r="E37" s="1" t="inlineStr">
+        <is>
+          <t>profit gain eps=-2</t>
+        </is>
+      </c>
+      <c r="F37" s="1" t="inlineStr">
+        <is>
+          <t>profit gain eps=-3</t>
+        </is>
+      </c>
+      <c r="G37" s="1" t="inlineStr">
+        <is>
+          <t>units change % (eps=-1)</t>
+        </is>
+      </c>
+      <c r="H37" s="1" t="inlineStr">
+        <is>
+          <t>units change % (eps=-2)</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="B38" t="n">
+        <v>1304279.56</v>
+      </c>
+      <c r="C38" t="n">
+        <v>1284473.94</v>
+      </c>
+      <c r="D38" t="n">
+        <v>1263583.5</v>
+      </c>
+      <c r="E38" t="n">
+        <v>1216613.87</v>
+      </c>
+      <c r="F38" t="n">
+        <v>1154884.9</v>
+      </c>
+      <c r="G38" t="n">
+        <v>-0.44</v>
+      </c>
+      <c r="H38" t="n">
+        <v>-0.95</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>80%</t>
+        </is>
+      </c>
+      <c r="B39" t="n">
+        <v>1252515.09</v>
+      </c>
+      <c r="C39" t="n">
+        <v>1207385.1</v>
+      </c>
+      <c r="D39" t="n">
+        <v>1155260.79</v>
+      </c>
+      <c r="E39" t="n">
+        <v>1028408.74</v>
+      </c>
+      <c r="F39" t="n">
+        <v>872702.01</v>
+      </c>
+      <c r="G39" t="n">
+        <v>-1.14</v>
+      </c>
+      <c r="H39" t="n">
+        <v>-2.66</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="B40" t="n">
+        <v>1104625.19</v>
+      </c>
+      <c r="C40" t="n">
+        <v>1021392.17</v>
+      </c>
+      <c r="D40" t="n">
+        <v>938688.7</v>
+      </c>
+      <c r="E40" t="n">
+        <v>775772.13</v>
+      </c>
+      <c r="F40" t="n">
+        <v>610863.35</v>
+      </c>
+      <c r="G40" t="n">
+        <v>-2.37</v>
+      </c>
+      <c r="H40" t="n">
+        <v>-4.7</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="B41" t="n">
+        <v>989526.74</v>
+      </c>
+      <c r="C41" t="n">
+        <v>904836.48</v>
+      </c>
+      <c r="D41" t="n">
+        <v>817978.41</v>
+      </c>
+      <c r="E41" t="n">
+        <v>635405.22</v>
+      </c>
+      <c r="F41" t="n">
+        <v>439124.85</v>
+      </c>
+      <c r="G41" t="n">
+        <v>-2.78</v>
+      </c>
+      <c r="H41" t="n">
+        <v>-5.74</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
           <t>40%</t>
         </is>
       </c>
-      <c r="B26" t="n">
+      <c r="B42" t="n">
         <v>836541.5</v>
       </c>
-      <c r="C26" t="n">
+      <c r="C42" t="n">
         <v>738604.8100000001</v>
       </c>
-      <c r="D26" t="n">
+      <c r="D42" t="n">
         <v>639382.25</v>
       </c>
-      <c r="E26" t="n">
+      <c r="E42" t="n">
         <v>442822.94</v>
       </c>
-      <c r="F26" t="n">
+      <c r="F42" t="n">
         <v>256002.06</v>
       </c>
-      <c r="G26" t="n">
+      <c r="G42" t="n">
         <v>-3.93</v>
       </c>
-      <c r="H26" t="n">
+      <c r="H42" t="n">
         <v>-7.84</v>
       </c>
     </row>
@@ -72966,7 +71981,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -73677,280 +72692,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:C20"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="58" customWidth="1" min="3" max="3"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>check</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>passed</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>detail</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Plan is complete: 30 products x 26 weeks, no missing price</t>
-        </is>
-      </c>
-      <c r="B2" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Replay is complete: 30 products x 52 weeks, no missing price</t>
-        </is>
-      </c>
-      <c r="B3" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Competitive band: every price within -8% ... +10% of the reference price</t>
-        </is>
-      </c>
-      <c r="B4" t="b">
-        <v>1</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>2340 prices; min -0.01%, max +10.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cost floor: every price above COGS + minimum markup + carrying cost + expected credit loss</t>
-        </is>
-      </c>
-      <c r="B5" t="b">
-        <v>1</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>smallest margin over floor $1.303</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Stability: no price moves more than 3% from the previous week</t>
-        </is>
-      </c>
-      <c r="B6" t="b">
-        <v>1</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>largest weekly move 3.00%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Credit D/E: never below the reference price (no discounts)</t>
-        </is>
-      </c>
-      <c r="B7" t="b">
-        <v>1</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>390 price-weeks in D/E categories: ['Beverages &amp; Cocoa']</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Credit C: markdown never deeper than 5%</t>
-        </is>
-      </c>
-      <c r="B8" t="b">
-        <v>1</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>1014 price-weeks</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>No markdown is ever applied in a peak-season week</t>
-        </is>
-      </c>
-      <c r="B9" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Hand calc Rule 1: 30% unserved in peak -&gt; +8.0%; 15% unserved in normal season -&gt; +3.0%; 4% unserved -&gt; 0%</t>
-        </is>
-      </c>
-      <c r="B10" t="b">
-        <v>1</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>0.080 / 0.030 / 0.000</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Hand calc Rule 3: 104 weeks cover off-peak -&gt; -10%; 26 weeks -&gt; 0; 52 weeks -&gt; -5%; peak -&gt; 0; rating D -&gt; 0; rating C -&gt; capped at -5%</t>
-        </is>
-      </c>
-      <c r="B11" t="b">
-        <v>1</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>0.100 / 0.000 / 0.050 / 0.000 / 0.000 / 0.050</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Rule 1 is monotone: more unserved demand never lowers the premium (all seasons)</t>
-        </is>
-      </c>
-      <c r="B12" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Rule 1 ordering: peak premium &gt;= normal &gt;= off-peak at the same scarcity</t>
-        </is>
-      </c>
-      <c r="B13" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Deterministic: re-running the engine gives identical prices</t>
-        </is>
-      </c>
-      <c r="B14" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Replay uses only information available at decision time (prices, stock and forecast inputs up to the origin week)</t>
-        </is>
-      </c>
-      <c r="B15" t="b">
-        <v>1</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>[{'origin': 208, 'last_week_used_for_prices': 208, 'last_week_used_for_stock': 208, 'last_week_used_for_forecast': 182}, {'origin': 234, 'last_week_used_for_prices': 234, 'last_week_used_for_stock': 234, 'last_week_used_for_forecast': 208}]</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>Simulated baseline reproduces the Part 2 expected sales within 5%</t>
-        </is>
-      </c>
-      <c r="B16" t="b">
-        <v>1</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-0.07%</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Benefit falls as customers become more price-sensitive (monotone in ε)</t>
-        </is>
-      </c>
-      <c r="B17" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>If customers ignore price (ε = 0) the engine can only add profit</t>
-        </is>
-      </c>
-      <c r="B18" t="b">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Sell-out protection: with scarcity-only pricing and stressed customers (ε = −2) expected units fall by at most 1% + 0.5 point</t>
-        </is>
-      </c>
-      <c r="B19" t="b">
-        <v>1</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>-0.47%</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>Reconciliation: money impact of the 780 rows equals the sum over products</t>
-        </is>
-      </c>
-      <c r="B20" t="b">
-        <v>1</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>